--- a/Daily_Status_Tasks_Update.xlsx
+++ b/Daily_Status_Tasks_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Shamshad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF06924B-6497-44BC-BE30-20553C885E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B874F2-34BC-4F4F-92FA-1BBE205D7A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="24">
   <si>
     <t>S.No</t>
   </si>
@@ -66,22 +66,37 @@
     <t>Points</t>
   </si>
   <si>
-    <t>Inprogress</t>
-  </si>
-  <si>
     <t>Certification</t>
   </si>
   <si>
     <t>Language</t>
   </si>
   <si>
-    <t>english,hindi</t>
-  </si>
-  <si>
-    <t>Pandas Filters Practice</t>
-  </si>
-  <si>
-    <t>Pandas:  .txt_files &amp; .excel_files</t>
+    <t xml:space="preserve">To Practice Excel sheet:-Two columns select,Compare </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> and hide &amp; unhide ,insert,delete in Stale_dependency report(4)</t>
+  </si>
+  <si>
+    <t>Google search Stale_Dependency_data_report(4)</t>
+  </si>
+  <si>
+    <t>Pandas</t>
+  </si>
+  <si>
+    <t>Some Data from the Titanic file</t>
+  </si>
+  <si>
+    <t>Applying Filters on it</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> .txt_files &amp; .excel_files Practice</t>
+  </si>
+  <si>
+    <t>DevOps</t>
+  </si>
+  <si>
+    <t>Step by Step Preparation to 4th Report</t>
   </si>
 </sst>
 </file>
@@ -400,14 +415,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.21875" customWidth="1"/>
     <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="34.33203125" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
     <col min="8" max="8" width="25.5546875" customWidth="1"/>
     <col min="9" max="9" width="17.77734375" customWidth="1"/>
@@ -455,16 +470,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -472,10 +484,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -483,10 +501,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -494,13 +512,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -508,16 +523,211 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
+        <v>45860</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>45860</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>45860</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45860</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>45861</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>45861</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>45861</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45861</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45862</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>45862</v>
+      </c>
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>45862</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
         <v>45863</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>45863</v>
+      </c>
+      <c r="C19" t="s">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>45863</v>
+      </c>
+      <c r="C20" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>45863</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Status_Tasks_Update.xlsx
+++ b/Daily_Status_Tasks_Update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Shamshad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B874F2-34BC-4F4F-92FA-1BBE205D7A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB58D73-62A2-438F-8EF1-D7A7C49DF34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="42">
   <si>
     <t>S.No</t>
   </si>
@@ -72,40 +72,101 @@
     <t>Language</t>
   </si>
   <si>
-    <t xml:space="preserve">To Practice Excel sheet:-Two columns select,Compare </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> and hide &amp; unhide ,insert,delete in Stale_dependency report(4)</t>
-  </si>
-  <si>
-    <t>Google search Stale_Dependency_data_report(4)</t>
-  </si>
-  <si>
     <t>Pandas</t>
   </si>
   <si>
-    <t>Some Data from the Titanic file</t>
-  </si>
-  <si>
-    <t>Applying Filters on it</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> .txt_files &amp; .excel_files Practice</t>
-  </si>
-  <si>
     <t>DevOps</t>
   </si>
   <si>
-    <t>Step by Step Preparation to 4th Report</t>
+    <t>english,hindi</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>reading</t>
+  </si>
+  <si>
+    <t>DevOps Project</t>
+  </si>
+  <si>
+    <t>Prepare Reports</t>
+  </si>
+  <si>
+    <t>learning</t>
+  </si>
+  <si>
+    <t>learning : Select Two Columns,compare,hide,unhide ,insert,delete in report(4)</t>
+  </si>
+  <si>
+    <t>I have Created 3rd Report (Cloud Configuration Report)</t>
+  </si>
+  <si>
+    <t>Google search &amp; Explore Cloud_Configuration_report(3),(Screen Shot)</t>
+  </si>
+  <si>
+    <t>Google search &amp; Explore  Stale_Dependency_data_report(4),(Screen Shot)</t>
+  </si>
+  <si>
+    <t>Step by Step explore &amp; Prepare to 4th Report</t>
+  </si>
+  <si>
+    <t>Download Titanic_data  &amp; Generate the Basic_Checks (Share to Screen Shot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pandas (.txt_files &amp; .excel_files ) Practice</t>
+  </si>
+  <si>
+    <t>Python Practice</t>
+  </si>
+  <si>
+    <t>Some Data from the Titanic file &amp; Applying Filters on it</t>
+  </si>
+  <si>
+    <t>Python Filters</t>
+  </si>
+  <si>
+    <t>lerning</t>
+  </si>
+  <si>
+    <t>Learning</t>
+  </si>
+  <si>
+    <t>Watching 4th report [Stale_Dependency_Data_Report(4)] Video</t>
+  </si>
+  <si>
+    <t>Inprogress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel Preparation in  Types  of  Pizzza's </t>
+  </si>
+  <si>
+    <t>To Prepare Excel sheet Non_Veg_Pizza_Price _Details</t>
+  </si>
+  <si>
+    <t>To Find out Non-Veg-Pizza-Prices from all Reataurents</t>
+  </si>
+  <si>
+    <t>To Prepare Excel sheet Non_Veg_Pizza _Price_Details</t>
+  </si>
+  <si>
+    <t>To Find out Non-Veg-Pizza-Prices from 100 Reataurents Complete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,9 +193,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,322 +480,758 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="54.33203125" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.5546875" customWidth="1"/>
-    <col min="9" max="9" width="17.77734375" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="14.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="83.6640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="25.5546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>45859</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>45859</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>45859</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>45859</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>45860</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>45860</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>45860</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>45860</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>45861</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D10" t="s">
-        <v>22</v>
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>45861</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>45861</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>45861</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>45862</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D14" t="s">
-        <v>18</v>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>45862</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="1">
         <v>46227</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="1">
         <v>45862</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="D17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>45863</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D18" t="s">
-        <v>19</v>
+      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>45863</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>45863</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>45863</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>14</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>45867</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>45867</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>45867</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>45867</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>45868</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <v>45868</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <v>45868</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>45868</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45869</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>45869</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>45869</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <v>45869</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Daily_Status_Tasks_Update.xlsx
+++ b/Daily_Status_Tasks_Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Shamshad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB58D73-62A2-438F-8EF1-D7A7C49DF34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AC58A8-D27B-4742-A492-E6D98F79E2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>S.No</t>
   </si>
@@ -151,6 +151,33 @@
   </si>
   <si>
     <t>To Find out Non-Veg-Pizza-Prices from 100 Reataurents Complete</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>Full day leave</t>
+  </si>
+  <si>
+    <t>Half day Leave</t>
+  </si>
+  <si>
+    <t>I am  watching an excel  3,4  videos</t>
+  </si>
+  <si>
+    <t>I am  watching an excel  1,2  videos</t>
+  </si>
+  <si>
+    <t>I am  watching an excel  5,6  videos</t>
+  </si>
+  <si>
+    <t>Excel Basic  Assignments</t>
+  </si>
+  <si>
+    <t>Some Tasks  Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining Tasks </t>
   </si>
 </sst>
 </file>
@@ -480,14 +507,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="3"/>
     <col min="2" max="2" width="14.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="25.77734375" style="3" customWidth="1"/>
     <col min="4" max="4" width="35.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="83.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="89.109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.21875" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="25.5546875" style="3" customWidth="1"/>
@@ -1230,6 +1257,334 @@
         <v>34</v>
       </c>
     </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <v>45873</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>45874</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>45874</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45874</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <v>45874</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <v>45875</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>45875</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>45875</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <v>45875</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <v>45876</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <v>45876</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <v>45876</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <v>45876</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <v>45877</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <v>45877</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <v>45877</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <v>45877</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
